--- a/sheets/조재수대금교본/검수/용두산 엘레지.xlsx
+++ b/sheets/조재수대금교본/검수/용두산 엘레지.xlsx
@@ -2382,8 +2382,7 @@
       <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">無
-南
-‹</t>
+南</t>
         </is>
       </c>
       <c r="E5" s="23"/>
@@ -2433,7 +2432,7 @@
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌∽</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E7" s="22"/>
@@ -2467,8 +2466,8 @@
       <c r="G8" s="23"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳ʒ
-㳞㴌ʒʒ</t>
+          <t xml:space="preserve">湳
+㳞㴌</t>
         </is>
       </c>
       <c r="I8" s="23"/>
@@ -2507,11 +2506,7 @@
         </is>
       </c>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
@@ -2564,8 +2559,7 @@
       <c r="C12" s="23"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌Z
-ZZ</t>
+          <t xml:space="preserve">㴌</t>
         </is>
       </c>
       <c r="E12" s="23"/>
@@ -2589,8 +2583,7 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰Z
-ZZ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -2610,20 +2603,15 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無Z
-ZZ</t>
+          <t xml:space="preserve">無</t>
         </is>
       </c>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ʒ
+          <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
@@ -2635,8 +2623,7 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南Z
-ZZ</t>
+          <t xml:space="preserve">南</t>
         </is>
       </c>
       <c r="E15" s="22"/>
@@ -2660,16 +2647,11 @@
       <c r="C16" s="23"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲Z
-ZZ</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="E16" s="23"/>
-      <c r="F16" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F16" s="21"/>
       <c r="G16" s="23"/>
       <c r="H16" s="21"/>
       <c r="I16" s="23"/>
@@ -2712,11 +2694,7 @@
       <c r="E18" s="24"/>
       <c r="F18" s="21"/>
       <c r="G18" s="24"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H18" s="21"/>
       <c r="I18" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/용두산 엘레지.xlsx
+++ b/sheets/조재수대금교본/검수/용두산 엘레지.xlsx
@@ -2432,7 +2432,7 @@
       <c r="C7" s="22"/>
       <c r="D7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌∽</t>
         </is>
       </c>
       <c r="E7" s="22"/>
@@ -2466,8 +2466,8 @@
       <c r="G8" s="23"/>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-㳞㴌</t>
+          <t xml:space="preserve">湳ʒ
+㳞㴌ʒʒ</t>
         </is>
       </c>
       <c r="I8" s="23"/>
@@ -2559,7 +2559,8 @@
       <c r="C12" s="23"/>
       <c r="D12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌</t>
+          <t xml:space="preserve">㴌Z
+ZZ</t>
         </is>
       </c>
       <c r="E12" s="23"/>
@@ -2583,7 +2584,8 @@
       <c r="C13" s="23"/>
       <c r="D13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰Z
+ZZ</t>
         </is>
       </c>
       <c r="E13" s="23"/>
@@ -2603,7 +2605,8 @@
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無</t>
+          <t xml:space="preserve">無Z
+ZZ</t>
         </is>
       </c>
       <c r="E14" s="24"/>
@@ -2611,7 +2614,7 @@
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
+          <t xml:space="preserve">汰ʒ
 無</t>
         </is>
       </c>
@@ -2623,7 +2626,8 @@
       <c r="C15" s="22"/>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南</t>
+          <t xml:space="preserve">南Z
+ZZ</t>
         </is>
       </c>
       <c r="E15" s="22"/>
@@ -2647,7 +2651,8 @@
       <c r="C16" s="23"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">仲Z
+ZZ</t>
         </is>
       </c>
       <c r="E16" s="23"/>

--- a/sheets/조재수대금교본/검수/용두산 엘레지.xlsx
+++ b/sheets/조재수대금교본/검수/용두산 엘레지.xlsx
@@ -2285,20 +2285,20 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16.2" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.2" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="16.2" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="16.2" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="90.91" customHeight="true">
+    <row r="2" ht="66.67" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2313,7 +2313,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="101.66" customHeight="true">
+    <row r="3" ht="74.45" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2344,7 +2344,7 @@
       </c>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" ht="101.66" customHeight="true">
+    <row r="4" ht="74.45" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2370,7 +2370,7 @@
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="101.66" customHeight="true">
+    <row r="5" ht="74.45" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
       <c r="H5" s="21"/>
       <c r="I5" s="23"/>
     </row>
-    <row r="6" ht="101.66" customHeight="true">
+    <row r="6" ht="74.45" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
       <c r="H6" s="21"/>
       <c r="I6" s="24"/>
     </row>
-    <row r="7" ht="101.66" customHeight="true">
+    <row r="7" ht="74.45" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="I7" s="22"/>
     </row>
-    <row r="8" ht="101.66" customHeight="true">
+    <row r="8" ht="74.45" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="23"/>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="I8" s="23"/>
     </row>
-    <row r="9" ht="101.66" customHeight="true">
+    <row r="9" ht="74.45" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="I9" s="23"/>
     </row>
-    <row r="10" ht="101.66" customHeight="true">
+    <row r="10" ht="74.45" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2518,7 +2518,7 @@
       <c r="H10" s="21"/>
       <c r="I10" s="24"/>
     </row>
-    <row r="11" ht="101.66" customHeight="true">
+    <row r="11" ht="74.45" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="I11" s="22"/>
     </row>
-    <row r="12" ht="101.66" customHeight="true">
+    <row r="12" ht="74.45" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2574,7 +2574,7 @@
       </c>
       <c r="I12" s="23"/>
     </row>
-    <row r="13" ht="101.66" customHeight="true">
+    <row r="13" ht="74.45" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2599,7 +2599,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="101.66" customHeight="true">
+    <row r="14" ht="74.45" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21"/>
       <c r="C14" s="24"/>
@@ -2620,7 +2620,7 @@
       </c>
       <c r="I14" s="24"/>
     </row>
-    <row r="15" ht="101.66" customHeight="true">
+    <row r="15" ht="74.45" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21"/>
       <c r="C15" s="22"/>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="I15" s="22"/>
     </row>
-    <row r="16" ht="101.66" customHeight="true">
+    <row r="16" ht="74.45" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -2661,7 +2661,7 @@
       <c r="H16" s="21"/>
       <c r="I16" s="23"/>
     </row>
-    <row r="17" ht="101.66" customHeight="true">
+    <row r="17" ht="74.45" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2682,7 +2682,7 @@
       <c r="H17" s="21"/>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" ht="101.66" customHeight="true">
+    <row r="18" ht="74.45" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -2708,6 +2708,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="44"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="60"/>
 </worksheet>
 </file>